--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-008_申請取下げ_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-008_申請取下げ_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="9725025"/>
+    <ext cx="8572500" cy="9925050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-008 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-008 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="64" customHeight="1">
+    <row r="3" ht="124" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2141,7 +2141,9 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：取下げ前が PENDING の場合に現在の承認者へ REQUEST_WITHDRAWN を通知（notify 4引数）、tables に approval_steps / users / notifications を追加、updated_at をトリガ自動更新に変更（@PreUpdate 記述を削除）</t>
+          <t>・確定設計変更 D1〜D10 を反映：取下げ前が PENDING の場合に現在の承認者へ REQUEST_WITHDRAWN を通知（notify 4引数）、tables に approval_steps / users / notifications を追加、updated_at をトリガ自動更新に変更（@PreUpdate 記述を削除）
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・Integer 同士の比較は == ではなく equals を使用</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3798,7 +3800,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public WithdrawResponse withdraw(@AuthenticationPrincipal Jwt jwt, @PathVariable Long id)</t>
+          <t>public WithdrawResponse withdraw(Authentication auth, @PathVariable Long id)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -3861,17 +3863,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン（sub = users.id）</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -3939,7 +3941,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return requestService.withdraw(id, userId);</t>
         </is>
       </c>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-008_申請取下げ_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-008_申請取下げ_オンライン詳細設計書.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-008 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-008 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1186,7 +1186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E41"/>
+  <dimension ref="A2:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1488,66 +1488,70 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の DRAFT / RETURNED を取り下げ</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>WITHDRAWN になる。attendance_breaks は変更されず、notify は呼ばれない</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>打刻は最終承認でのみ変わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>9.2 RequestController（MockMvc / API テスト）</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>本人の PENDING に POST</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>200、{"status":"WITHDRAWN"}</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -1557,24 +1561,20 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>POST /api/requests/abc/withdraw</t>
+          <t>本人の PENDING に POST</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>400 E-002</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>500 にならない</t>
-        </is>
-      </c>
+          <t>200、{"status":"WITHDRAWN"}</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1589,99 +1589,103 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
+          <t>POST /api/requests/abc/withdraw</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>400 E-002</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>500 にならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
           <t>取下げ不可の状態／他人の申請</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>409 E-011／403 E-010</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Authorization なし</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>9.3 結合テスト（実 DB）</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>取下げ後に ONL-006 で一覧取得</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>該当申請が status=WITHDRAWN で表示される</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr"/>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -1696,40 +1700,40 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
+          <t>取下げ後に ONL-006 で一覧取得</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>該当申請が status=WITHDRAWN で表示される</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
           <t>取下げ後に approval_steps を確認</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>WAITING のまま変化なし。ONL-007 の steps[].current は全て false</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>境界</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>取下げと承認（ONL-010）を同時に実行</t>
-        </is>
-      </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>どちらか一方のみ成功。承認が先なら取下げは E-011、取下げが先なら承認は E-011</t>
+          <t>DB の status は WAITING のまま変化なし（更新されない）。ONL-007 で取得すると steps[].status は "SKIPPED"、steps[].current は全て false</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>行ロックの確認</t>
+          <t>SKIPPED は表示専用（DB に保存しない）</t>
         </is>
       </c>
     </row>
@@ -1741,137 +1745,137 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>取下げと承認（ONL-010）を同時に実行</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>どちらか一方のみ成功。承認が先なら取下げは E-011、取下げが先なら承認は E-011</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>行ロックの確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>ONL-005 の下書き保存 → 取下げ</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>WITHDRAWN。以後その下書きは重複判定に影響しない</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>取下げ後に ONL-007 で GET（本人）</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>200。steps[].status は取下げ時点で WAITING だったステップのみ "SKIPPED"（APPROVED だった 1 段目はそのまま APPROVED）、current は全て false</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>displayStatus の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>9.4 RequestService#withdraw  通知（Mockito でモック）</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>本人の PENDING（current_step=1、approver_id=上長）を取り下げ</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>notify(上長ID, REQUEST_WITHDRAWN, 本文, 申請ID) が1回</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>本文に申請者名・申請種別・期間を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>本人の PENDING（current_step=2、approver_id=NULL）。有効な管理者が2名</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>notify が管理者2名に各1回（requestId 同一）</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>申請者が ADMIN の場合は本人を除く</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>本人の DRAFT／RETURNED を取り下げ</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>notify は呼ばれない</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>承認者の手元にないため</t>
         </is>
       </c>
     </row>
@@ -1883,162 +1887,243 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>本人の PENDING（current_step=2、approver_id=NULL）。有効な管理者が2名</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>notify が管理者2名に各1回（requestId 同一）</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>申請者が ADMIN の場合は本人を除く</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>本人の DRAFT／RETURNED を取り下げ</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>notify は呼ばれない</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>承認者の手元にないため</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
           <t>境界</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>PENDING だが通知先が 0 件</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>取下げは成功（WITHDRAWN）、notify は呼ばれない</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>エラーにしない</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="49" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+    <row r="37" ht="49" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>notify が例外（IllegalArgumentException）</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>例外が伝播し、トランザクションがロールバックされる（結合テストで status が PENDING のまま）</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>E-012</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>E-010 / E-011 の場合</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>notify は呼ばれない</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="49" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の PENDING（current_step=1・上長あり）を取り下げ</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>notify(上長ID, REQUEST_WITHDRAWN, 「…さんが休憩・離席修正申請（対象日）を取り下げました。」, 申請ID) が 1 回</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>文面の種別名・期間（開始日＝終了日なので日付 1 つ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>9.5 結合テスト（実 DB）  通知</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="10" t="n"/>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="49" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+    <row r="43" ht="49" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>PENDING を取下げ後、notifications を確認</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>type=REQUEST_WITHDRAWN、request_id=申請ID、is_read=FALSE の行が承認者ごとに1行</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>fk_notifications_request_id を満たす</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>取下げ後に requests.updated_at を確認</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>取下げ前より新しい（トリガで更新）</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>アプリは updated_at を設定しない</t>
         </is>
@@ -2046,11 +2131,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A38:E38"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2063,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2147,6 +2232,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="94" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>表示ステータス SKIPPED と休憩・離席修正申請に対応：取下げでは approval_steps（WAITING）を更新せず、ONL-007 が「申請が PENDING でないのに WAITING のままのステップ」を表示用の SKIPPED（画面「処理なし」）として返す旨を追記（DB の値は変更しない）。取下げ通知の文面に休憩・離席修正申請を追加。WITHDRAWABLE は RequestService 内の private 定数である実装に合わせて記述を修正。テスト観点を更新</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2247,7 +2355,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>目的</t>
@@ -2255,7 +2363,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>承認前（下書き・承認待ち・差戻し）の自分の申請を取下げ状態（WITHDRAWN）にする。取り下げた申請は終了状態となり、承認フローの対象から外れる。</t>
+          <t>承認前（下書き・承認待ち・差戻し）の自分の申請（休暇・打刻修正・休憩離席修正）を取下げ状態（WITHDRAWN）にする。取り下げた申請は終了状態となり、承認フローの対象から外れる。承認待ちだった場合に残る WAITING の承認ステップは DB では更新せず、詳細取得（ONL-007）が表示用の状態 SKIPPED（画面は「処理なし」）として返す。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -2295,7 +2403,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="49" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>事後条件</t>
@@ -2303,7 +2411,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>requests.status = WITHDRAWN（updated_at は DB トリガで自動更新）。approval_steps は更新しない（WAITING のステップは申請状態が PENDING でなくなることで無効扱いとなる）。休暇残日数は未消化のため変更なし。取下げ前の status が PENDING だった場合のみ、現在の承認者へ画面内通知（type=REQUEST_WITHDRAWN、requestId=申請ID）を登録する。DRAFT / RETURNED の取下げでは通知しない（承認者の手元に無いため）。</t>
+          <t>requests.status = WITHDRAWN（updated_at は DB トリガで自動更新）。approval_steps は更新しない（WAITING のステップは DB 上は WAITING のまま残り、申請状態が PENDING でなくなることで無効扱いとなる。ONL-007 はこれを表示状態 SKIPPED＝画面「処理なし」として返す）。休暇残日数・打刻（attendance_records / attendance_breaks）は変更しない。取下げ前の status が PENDING だった場合のみ、現在の承認者へ画面内通知（type=REQUEST_WITHDRAWN、requestId=申請ID）を登録する。DRAFT / RETURNED の取下げでは通知しない（承認者の手元に無いため）。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -2435,7 +2543,7 @@
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="10" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>KF-BD-005</t>
@@ -2448,7 +2556,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>申請種別・申請状態・取得単位・承認ステップ状態・申請状態遷移</t>
+          <t>申請種別・申請状態・取得単位・承認ステップ状態（WAITING / APPROVED / RETURNED / REJECTED。ONL-007 の応答では表示用 SKIPPED）・申請状態遷移</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -2595,7 +2703,7 @@
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>ONL-007</t>
@@ -2608,7 +2716,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>GlobalExceptionHandler#handleTypeMismatch、forbidden() の方針</t>
+          <t>GlobalExceptionHandler#handleTypeMismatch、forbidden() の方針。取下げ後の WAITING ステップは ONL-007 が SKIPPED（処理なし）として返す（displayStatus）</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -2935,7 +3043,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1">
+    <row r="40" ht="79" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>entity</t>
@@ -2953,7 +3061,7 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>WITHDRAWN / WITHDRAWABLE / PENDING</t>
+          <t>WITHDRAWN / PENDING などの状態定数（変更なし）。WITHDRAWABLE（DRAFT, PENDING, RETURNED）は RequestService 内の private 定数</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -3618,7 +3726,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>④</t>
@@ -3632,7 +3740,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>RequestStatus.WITHDRAWABLE に含まれるか。APPROVED / REJECTED / WITHDRAWN は不可</t>
+          <t>WITHDRAWABLE（RequestService 内の private 定数：DRAFT / PENDING / RETURNED）に含まれるか。APPROVED / REJECTED / WITHDRAWN は不可</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3643,7 +3751,7 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="64" customHeight="1">
+    <row r="8" ht="79" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>⑤</t>
@@ -3656,7 +3764,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>UPDATE requests SET status = 'WITHDRAWN'（updated_at は DB トリガで自動更新）。approval_steps は更新しない。更新前の status を fromStatus に退避する</t>
+          <t>UPDATE requests SET status = 'WITHDRAWN'（updated_at は DB トリガで自動更新）。approval_steps は更新しない。更新前の status を fromStatus に退避する（承認ステップは WAITING のまま残り、ONL-007 が表示状態 SKIPPED として返す）</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -3753,7 +3861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F57"/>
+  <dimension ref="A2:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4152,7 +4260,7 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="439" customHeight="1">
+    <row r="26" ht="469" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -4165,14 +4273,14 @@
     if (!r.getUserId().equals(userId))                                     // ③ 他人の申請 → E-010
         throw forbidden();
     String fromStatus = r.getStatus();                                     // 更新前の status を退避
-    if (!RequestStatus.WITHDRAWABLE.contains(fromStatus))                  // ④ 取下げ不可の状態 → E-011
+    if (!WITHDRAWABLE.contains(fromStatus))                  // ④ 取下げ不可の状態 → E-011
         throw new BusinessException("E-011", "この申請は既に処理されています。", HttpStatus.CONFLICT);
     r.setStatus(RequestStatus.WITHDRAWN);                                  // ⑤
     requestRepository.save(r);                                             //   UPDATE requests SET status = 'WITHDRAWN' WHERE id = ?（updated_at はトリガ）
     if (RequestStatus.PENDING.equals(fromStatus)) {                        // ⑥ 承認待ちだった場合のみ通知
         User applicant = userRepository.findById(userId).orElseThrow(RequestService::forbidden);
         ApprovalStep current = approvalStepRepository.findByRequestIdOrderByStepNo(requestId).stream()
-                .filter(s -&gt; s.getStepNo() == r.getCurrentStep())          // 現在の承認ステップ（1 or 2）
+                .filter(s -&gt; s.getStepNo().equals(r.getCurrentStep()))          // 現在の承認ステップ（1 or 2）
                 .findFirst().orElse(null);                                 // 無ければ通知しない
         if (current != null) {
             String msg = buildWithdrawnMessage(applicant, r);
@@ -4183,8 +4291,9 @@
     log.info("[ONL-008] request withdrawn id={} userId={} fromStatus={}", requestId, userId, fromStatus);
     return new WithdrawResponse(r.getStatus());                            // ⑦
 private String buildWithdrawnMessage(User applicant, Request r):
-    // 例: 「山田 太郎さんが休暇申請（2026-10-14〜2026-10-16）を取り下げました。」
-    kind = LEAVE.equals(r.getRequestType()) ? "休暇申請" : "打刻修正申請";
+    // 例: 「山田 太郎さんが休暇申請（2026-10-14〜2026-10-16）を取り下げました。」／「山田 太郎さんが休憩・離席修正申請（2026-10-01）を取り下げました。」
+    kind = LEAVE.equals(r.getRequestType()) ? "休暇申請"
+           : (BREAK_CORRECTION.equals(r.getRequestType()) ? "休憩・離席修正申請" : "打刻修正申請");
     period = r.getStartDate().equals(r.getEndDate()) ? r.getStartDate() : r.getStartDate() + "〜" + r.getEndDate();
     return applicant.getName() + "さんが" + kind + "（" + period + "）を取り下げました。";</t>
         </is>
@@ -4210,7 +4319,7 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
-    <row r="28" ht="94" customHeight="1">
+    <row r="28" ht="169" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -4222,7 +4331,9 @@
 WITHDRAWN の再取下げは WITHDRAWABLE に含まれないため E-011（二重クリックでも安全）。
 forbidden() は ONL-005 の RequestService 内 private static メソッド（E-010 / 403）。
 通知は取下げ前が PENDING の場合のみ。1段目承認待ちは上長、2段目承認待ちは有効な全管理者（申請者本人を除く）が宛先。type=REQUEST_WITHDRAWN は ONL-005 の NotificationType に定義済み。
-updated_at は DB トリガ（BEFORE UPDATE）が更新するためアプリは設定しない。</t>
+updated_at は DB トリガ（BEFORE UPDATE）が更新するためアプリは設定しない。
+【承認ステップは更新しない（SKIPPED）】取下げでは approval_steps を更新しない（status は WAITING のまま）。画面が「承認待ち」と誤解しないよう、ONL-007 の RequestService#displayStatus が「DB が WAITING かつ申請が PENDING でない」ステップを表示状態 SKIPPED（画面は「処理なし」）に置き換え、current も false にする。DB の値は変わらないので、再提出（ONL-022）では旧ステップが削除される。
+【文面の種別名】LEAVE=「休暇申請」、BREAK_CORRECTION=「休憩・離席修正申請」、それ以外（CLOCK_CORRECTION）=「打刻修正申請」。期間は開始日＝終了日なら日付 1 つ（打刻修正・休憩離席修正は常に 1 つ）。</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
@@ -4488,7 +4599,7 @@
       <c r="E46" s="9" t="n"/>
       <c r="F46" s="10" t="n"/>
     </row>
-    <row r="47" ht="19" customHeight="1">
+    <row r="47" ht="34" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>ONL-007</t>
@@ -4496,7 +4607,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>steps[].current は申請が PENDING のときのみ true（実装済み）</t>
+          <t>steps[].current は申請が PENDING のときのみ true。申請が PENDING でなく DB が WAITING のステップは steps[].status を SKIPPED（画面「処理なし」）として返す（実装済み。RequestService#displayStatus）</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -4588,7 +4699,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="34" customHeight="1">
+    <row r="53" ht="79" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>D-3</t>
@@ -4601,14 +4712,14 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>更新しない。申請状態が PENDING でないことで無効扱い（KF-DD-001「申請状態で判定」）</t>
+          <t>更新しない。申請状態が PENDING でないことで無効扱い（KF-DD-001「申請状態で判定」）。画面表示は ONL-007 が WAITING を SKIPPED（処理なし）に変換して返す</t>
         </is>
       </c>
       <c r="D53" s="9" t="n"/>
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>ONL-009〜012 が status = PENDING を条件にすること（上表）</t>
+          <t>ONL-009〜012 が status = PENDING を条件にすること（上表）。DB の WAITING は残るが、ONL-007 の表示では SKIPPED になり承認待ちと誤認されない</t>
         </is>
       </c>
     </row>
@@ -4708,8 +4819,32 @@
         </is>
       </c>
     </row>
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請の取下げ</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION も他種別と同様に DRAFT / PENDING / RETURNED から取り下げられる。通知の文面は「休憩・離席修正申請」</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>打刻（attendance_breaks）の変更は最終承認（ONL-010）でのみ行われるため、取下げ時に打刻の巻き戻しは不要</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="53">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="C54:E54"/>
@@ -4750,6 +4885,7 @@
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C58:E58"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="B6:F6"/>
@@ -4774,7 +4910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F61"/>
+  <dimension ref="A2:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4905,7 +5041,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>request_type</t>
@@ -4928,12 +5064,12 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>—（読み込みのみ）</t>
+          <t>○ 通知文面の種別名（読み込みのみ）</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION（ck_req_type）</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION（ck_req_type）</t>
         </is>
       </c>
     </row>
@@ -4992,16 +5128,16 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>○ 通知文面（期間）</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>休暇の開始日／打刻修正の対象日</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1">
+          <t>休暇の開始日／打刻修正・休憩離席修正の対象日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>end_date</t>
@@ -5024,12 +5160,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>○ 通知文面（期間）</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>休暇の終了日／打刻修正は startDate と同値</t>
+          <t>休暇の終了日／打刻修正・休憩離席修正は startDate と同値</t>
         </is>
       </c>
     </row>
@@ -5161,487 +5297,487 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>corrected_break_kind / start / end</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>correctedBreakKind / Start / End</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>String / LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION のみ。取下げでは参照・変更しない（V5 で追加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>○ 状態確認／○ WITHDRAWN に更新</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN（ck_req_status）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>current_step</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>currentStep</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>変更しない</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>現在の承認段。DRAFT は 0、提出後は 1 または 2</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>current_step</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>currentStep</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>変更しない</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>現在の承認段。DRAFT は 0、提出後は 1 または 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>submitted_at</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>submittedAt</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>変更しない</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>提出日時（JST）。DRAFT は NULL</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_requests_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>■ approval_steps</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>IDENTITY 自動採番</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>requestId</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>○ 検索条件</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>FK requests。findByRequestIdOrderByStepNo</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="49" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26" ht="49" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>step_no</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>stepNo</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>○ 現在の承認ステップの特定（= requests.current_step）</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>1: 上長 / 2: 管理者</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>approver_id</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>approverId</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>○ 通知先の特定（1段目）</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>2段目は NULL → 有効な全管理者へ通知</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28" ht="49" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>—（読み込みのみ）</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>WAITING / APPROVED / RETURNED / REJECTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>—（読み込みのみ。更新しない）</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>WAITING / APPROVED / RETURNED / REJECTED。取下げ後も WAITING のまま。ONL-007 の応答では SKIPPED（表示専用）に変換される</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>■ notifications</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>—（INSERT 後に採番）</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>userId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -5656,61 +5792,61 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>○ 登録（現在の承認者）</t>
+          <t>—（INSERT 後に採番）</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>NotificationService#notify が INSERT</t>
+          <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>○ 登録（REQUEST_WITHDRAWN）</t>
+          <t>○ 登録（現在の承認者）</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>NotificationService#notify が INSERT</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -5720,366 +5856,366 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>○ 登録（取り下げた申請の ID）</t>
+          <t>○ 登録（REQUEST_WITHDRAWN）</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>FK requests(id)</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>requestId</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>○ 登録（取り下げた申請の ID）</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>FK requests(id)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>message</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>○ 登録（取下げ通知の文面）</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(500)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>is_read</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>○ 登録（FALSE）</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>BOOLEAN、既定 FALSE</t>
         </is>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>is_read</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>○ 登録（FALSE）</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>BOOLEAN、既定 FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="64" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_notifications_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>■ users</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="10" t="n"/>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>○ 検索条件（申請者名の取得）</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番（FOR UPDATE で行ロック）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
           <t>password_hash</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>passwordHash</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>BCrypt ハッシュ。VARCHAR(255)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>○ 通知文面（申請者名）</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>EMPLOYEE / MANAGER / ADMIN</t>
         </is>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>departmentId</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -6089,19 +6225,19 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>FK departments</t>
+          <t>EMPLOYEE / MANAGER / ADMIN</t>
         </is>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>manager_id</t>
+          <t>department_id</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>managerId</t>
+          <t>departmentId</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -6121,29 +6257,29 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>FK users（自己参照）。1段目承認者の決定に使用</t>
+          <t>FK departments</t>
         </is>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>hire_date</t>
+          <t>manager_id</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>hireDate</t>
+          <t>managerId</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -6151,127 +6287,143 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>FK users（自己参照）。1段目承認者の決定に使用</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
+          <t>hire_date</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>hireDate</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>ACTIVE / INACTIVE（既定 ACTIVE）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n"/>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="10" t="n"/>
-    </row>
-    <row r="53" ht="49" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM requests WHERE id = ? FOR UPDATE</t>
-        </is>
-      </c>
+      <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="n"/>
       <c r="D53" s="9" t="n"/>
       <c r="E53" s="9" t="n"/>
@@ -6280,12 +6432,12 @@
     <row r="54" ht="49" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>状態の更新（RequestRepository#save → Dirty Checking）</t>
+          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>UPDATE requests SET status = 'WITHDRAWN' WHERE id = ?   -- 変更した列のみ。updated_at は DB トリガ trg_requests_updated_at で自動更新。Hibernate の設定により全列更新になる場合がある</t>
+          <t>SELECT * FROM requests WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
       <c r="C54" s="9" t="n"/>
@@ -6293,15 +6445,15 @@
       <c r="E54" s="9" t="n"/>
       <c r="F54" s="10" t="n"/>
     </row>
-    <row r="55" ht="64" customHeight="1">
+    <row r="55" ht="49" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>現在の承認ステップの取得（ApprovalStepRepository#findByRequestIdOrderByStepNo）</t>
+          <t>状態の更新（RequestRepository#save → Dirty Checking）</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM approval_steps WHERE request_id = ? ORDER BY step_no   -- 取下げ前が PENDING のときのみ</t>
+          <t>UPDATE requests SET status = 'WITHDRAWN' WHERE id = ?   -- 変更した列のみ。updated_at は DB トリガ trg_requests_updated_at で自動更新。Hibernate の設定により全列更新になる場合がある</t>
         </is>
       </c>
       <c r="C55" s="9" t="n"/>
@@ -6312,12 +6464,12 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>管理者の取得（2段目承認待ちのとき。UserRepository#findByRoleAndStatus）</t>
+          <t>現在の承認ステップの取得（ApprovalStepRepository#findByRequestIdOrderByStepNo）</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
+          <t>SELECT * FROM approval_steps WHERE request_id = ? ORDER BY step_no   -- 取下げ前が PENDING のときのみ</t>
         </is>
       </c>
       <c r="C56" s="9" t="n"/>
@@ -6328,13 +6480,12 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>通知の登録（NotificationService#notify → NotificationRepository#save）</t>
+          <t>管理者の取得（2段目承認待ちのとき。UserRepository#findByRoleAndStatus）</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO notifications (user_id, type, request_id, message, is_read)
-  VALUES (?, 'REQUEST_WITHDRAWN', ?, ?, FALSE)   -- 宛先の人数分</t>
+          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
         </is>
       </c>
       <c r="C57" s="9" t="n"/>
@@ -6342,84 +6493,101 @@
       <c r="E57" s="9" t="n"/>
       <c r="F57" s="10" t="n"/>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>通知の登録（NotificationService#notify → NotificationRepository#save）</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO notifications (user_id, type, request_id, message, is_read)
+  VALUES (?, 'REQUEST_WITHDRAWN', ?, ?, FALSE)   -- 宛先の人数分</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>7.3 設定値</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="10" t="n"/>
-    </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F60" s="10" t="n"/>
-    </row>
-    <row r="61" ht="49" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="F61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="49" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Asia/Tokyo</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>ONL-005 と共通</t>
         </is>
       </c>
-      <c r="F61" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="B54:F54"/>
-    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="C61:D61"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="E60:F60"/>
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B57:F57"/>
+    <mergeCell ref="A53:F53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
